--- a/Spend as percentage.xlsx
+++ b/Spend as percentage.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://inbetgroup-my.sharepoint.com/personal/kostadin_radkov_inbet_com/Documents/Mexico/Audit/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8e224380099ec4b3/Documents/FinanceMX/MX_Finance/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1034" documentId="8_{5861C6C4-333F-4F3B-B0FE-C9E2151B6F12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38D37A7A-7922-44AE-B736-DE9B5294127C}"/>
+  <xr:revisionPtr revIDLastSave="1035" documentId="8_{5861C6C4-333F-4F3B-B0FE-C9E2151B6F12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65AE4836-97BC-44B3-B09B-E331EAE7B10E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{2A262237-2F11-43D0-ACD0-6DB147DC098E}"/>
+    <workbookView xWindow="972" yWindow="1224" windowWidth="20520" windowHeight="12456" xr2:uid="{2A262237-2F11-43D0-ACD0-6DB147DC098E}"/>
   </bookViews>
   <sheets>
     <sheet name="Simulation" sheetId="10" r:id="rId1"/>
@@ -982,7 +982,7 @@
     <numFmt numFmtId="166" formatCode="#,##0.00\ [$€-1]"/>
     <numFmt numFmtId="167" formatCode="[$€-2]\ #,##0.00"/>
     <numFmt numFmtId="168" formatCode="[$€-2]\ #,##0.00;[Red]\-[$€-2]\ #,##0.00"/>
-    <numFmt numFmtId="171" formatCode="0.0000%"/>
+    <numFmt numFmtId="169" formatCode="0.0000%"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
@@ -2062,6 +2062,77 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="7" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="7" fillId="0" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="7" fillId="8" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="7" fillId="8" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="7" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="8" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="8" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2128,164 +2199,98 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="7" fillId="8" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="7" fillId="8" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="7" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="7" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="7" fillId="0" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="7" fillId="8" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="7" fillId="8" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="7" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="7" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="7" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="8" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="8" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="7" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="7" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="7" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="7" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="7" fillId="8" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="7" fillId="8" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="7" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2295,11 +2300,6 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="1" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="1" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="7" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -2704,7 +2704,7 @@
         <v>259</v>
       </c>
       <c r="C11" s="72">
-        <v>2.5000000000000001E-2</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="12" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="C13" s="128">
         <f>C9/C11</f>
-        <v>26666666.666666668</v>
+        <v>22222222.222222224</v>
       </c>
     </row>
   </sheetData>
@@ -2889,10 +2889,10 @@
       <c r="I8" s="116"/>
     </row>
     <row r="9" spans="2:12" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C9" s="136" t="s">
+      <c r="C9" s="161" t="s">
         <v>249</v>
       </c>
-      <c r="D9" s="136"/>
+      <c r="D9" s="161"/>
       <c r="E9" s="96"/>
       <c r="F9">
         <v>4.8300000000000003E-2</v>
@@ -2905,50 +2905,50 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="159" t="s">
+      <c r="C10" s="137" t="s">
         <v>147</v>
       </c>
-      <c r="D10" s="160"/>
-      <c r="E10" s="161">
+      <c r="D10" s="138"/>
+      <c r="E10" s="139">
         <v>46082</v>
       </c>
-      <c r="F10" s="162"/>
-      <c r="G10" s="163">
+      <c r="F10" s="140"/>
+      <c r="G10" s="141">
         <v>46113</v>
       </c>
-      <c r="H10" s="164"/>
-      <c r="I10" s="161">
+      <c r="H10" s="142"/>
+      <c r="I10" s="139">
         <v>46143</v>
       </c>
-      <c r="J10" s="165"/>
+      <c r="J10" s="143"/>
     </row>
     <row r="11" spans="2:12" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C11" s="166" t="s">
+      <c r="C11" s="144" t="s">
         <v>148</v>
       </c>
-      <c r="D11" s="167"/>
-      <c r="E11" s="168">
+      <c r="D11" s="145"/>
+      <c r="E11" s="146">
         <f>5444466*F9</f>
         <v>262967.70780000003</v>
       </c>
-      <c r="F11" s="169"/>
-      <c r="G11" s="170">
+      <c r="F11" s="147"/>
+      <c r="G11" s="148">
         <f>4985574*H9</f>
         <v>243296.01120000001</v>
       </c>
-      <c r="H11" s="171"/>
-      <c r="I11" s="168">
+      <c r="H11" s="149"/>
+      <c r="I11" s="146">
         <f>2965798*J9</f>
         <v>146510.42120000001</v>
       </c>
-      <c r="J11" s="172"/>
+      <c r="J11" s="150"/>
       <c r="L11">
         <v>95686</v>
       </c>
     </row>
     <row r="12" spans="2:12" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C12" s="173"/>
-      <c r="D12" s="174"/>
+      <c r="C12" s="151"/>
+      <c r="D12" s="152"/>
       <c r="E12" s="55" t="s">
         <v>149</v>
       </c>
@@ -2969,13 +2969,13 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="156" t="s">
+      <c r="B13" s="134" t="s">
         <v>235</v>
       </c>
-      <c r="C13" s="215" t="s">
+      <c r="C13" s="153" t="s">
         <v>248</v>
       </c>
-      <c r="D13" s="176"/>
+      <c r="D13" s="154"/>
       <c r="E13" s="102">
         <f>1444502*F9</f>
         <v>69769.44660000001</v>
@@ -3002,11 +3002,11 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="157"/>
-      <c r="C14" s="154" t="s">
+      <c r="B14" s="135"/>
+      <c r="C14" s="155" t="s">
         <v>150</v>
       </c>
-      <c r="D14" s="155"/>
+      <c r="D14" s="156"/>
       <c r="E14" s="103">
         <f>'Calc - opperational'!G6*F9</f>
         <v>21905.596566000004</v>
@@ -3033,11 +3033,11 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="157"/>
-      <c r="C15" s="154" t="s">
+      <c r="B15" s="135"/>
+      <c r="C15" s="155" t="s">
         <v>239</v>
       </c>
-      <c r="D15" s="155"/>
+      <c r="D15" s="156"/>
       <c r="E15" s="103">
         <f>'Calc - opperational'!G11*F9</f>
         <v>531.30000000000007</v>
@@ -3064,11 +3064,11 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="157"/>
-      <c r="C16" s="154" t="s">
+      <c r="B16" s="135"/>
+      <c r="C16" s="155" t="s">
         <v>242</v>
       </c>
-      <c r="D16" s="155"/>
+      <c r="D16" s="156"/>
       <c r="E16" s="103">
         <f>'Calc - opperational'!D14*F9</f>
         <v>8953.4675999999999</v>
@@ -3095,11 +3095,11 @@
       </c>
     </row>
     <row r="17" spans="2:10" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="158"/>
-      <c r="C17" s="154" t="s">
+      <c r="B17" s="136"/>
+      <c r="C17" s="155" t="s">
         <v>238</v>
       </c>
-      <c r="D17" s="155"/>
+      <c r="D17" s="156"/>
       <c r="E17" s="104">
         <f>E11*F17</f>
         <v>31556.124936000004</v>
@@ -3123,11 +3123,11 @@
       </c>
     </row>
     <row r="18" spans="2:10" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="137" t="s">
+      <c r="B18" s="162" t="s">
         <v>234</v>
       </c>
-      <c r="C18" s="138"/>
-      <c r="D18" s="139"/>
+      <c r="C18" s="163"/>
+      <c r="D18" s="164"/>
       <c r="E18" s="105">
         <f>SUM(E14:E17)</f>
         <v>62946.489102000007</v>
@@ -3154,13 +3154,13 @@
       </c>
     </row>
     <row r="19" spans="2:10" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="151" t="s">
+      <c r="B19" s="176" t="s">
         <v>236</v>
       </c>
-      <c r="C19" s="154" t="s">
+      <c r="C19" s="155" t="s">
         <v>4</v>
       </c>
-      <c r="D19" s="155"/>
+      <c r="D19" s="156"/>
       <c r="E19" s="103">
         <f>'Calc - opperational'!D23*F9</f>
         <v>76409.520012000008</v>
@@ -3187,11 +3187,11 @@
       </c>
     </row>
     <row r="20" spans="2:10" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="152"/>
-      <c r="C20" s="154" t="s">
+      <c r="B20" s="177"/>
+      <c r="C20" s="155" t="s">
         <v>151</v>
       </c>
-      <c r="D20" s="155"/>
+      <c r="D20" s="156"/>
       <c r="E20" s="103">
         <f>'Calc - opperational'!D31*F9</f>
         <v>10317.806877000001</v>
@@ -3218,11 +3218,11 @@
       </c>
     </row>
     <row r="21" spans="2:10" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="152"/>
-      <c r="C21" s="154" t="s">
+      <c r="B21" s="177"/>
+      <c r="C21" s="155" t="s">
         <v>152</v>
       </c>
-      <c r="D21" s="155"/>
+      <c r="D21" s="156"/>
       <c r="E21" s="103">
         <f>'Calc - opperational'!D42*F9</f>
         <v>82355.807393999989</v>
@@ -3249,11 +3249,11 @@
       </c>
     </row>
     <row r="22" spans="2:10" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="152"/>
-      <c r="C22" s="154" t="s">
+      <c r="B22" s="177"/>
+      <c r="C22" s="155" t="s">
         <v>153</v>
       </c>
-      <c r="D22" s="155"/>
+      <c r="D22" s="156"/>
       <c r="E22" s="103">
         <f>'Calc - opperational'!D49*F9</f>
         <v>679.52545500000008</v>
@@ -3280,11 +3280,11 @@
       </c>
     </row>
     <row r="23" spans="2:10" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="153"/>
-      <c r="C23" s="154" t="s">
+      <c r="B23" s="178"/>
+      <c r="C23" s="155" t="s">
         <v>154</v>
       </c>
-      <c r="D23" s="155"/>
+      <c r="D23" s="156"/>
       <c r="E23" s="103">
         <f>'Calc - opperational'!D52*F9</f>
         <v>5341.2511530000002</v>
@@ -3311,11 +3311,11 @@
       </c>
     </row>
     <row r="24" spans="2:10" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="137" t="s">
+      <c r="B24" s="162" t="s">
         <v>237</v>
       </c>
-      <c r="C24" s="138"/>
-      <c r="D24" s="139"/>
+      <c r="C24" s="163"/>
+      <c r="D24" s="164"/>
       <c r="E24" s="106">
         <f>E23+E22+E21+E20+E19</f>
         <v>175103.91089100001</v>
@@ -3342,64 +3342,49 @@
       </c>
     </row>
     <row r="25" spans="2:10" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="140" t="s">
+      <c r="B25" s="165" t="s">
         <v>240</v>
       </c>
-      <c r="C25" s="141"/>
-      <c r="D25" s="142"/>
-      <c r="E25" s="132">
+      <c r="C25" s="166"/>
+      <c r="D25" s="167"/>
+      <c r="E25" s="157">
         <f>E24+E18+E13</f>
         <v>307819.84659300005</v>
       </c>
-      <c r="F25" s="145">
+      <c r="F25" s="170">
         <f>E25/$E$11</f>
         <v>1.1705613938997874</v>
       </c>
-      <c r="G25" s="147">
+      <c r="G25" s="172">
         <f>G24+G18+G13</f>
         <v>309354.50500800001</v>
       </c>
-      <c r="H25" s="149">
+      <c r="H25" s="174">
         <f>G25/G$11</f>
         <v>1.2715149068091256</v>
       </c>
-      <c r="I25" s="132">
+      <c r="I25" s="157">
         <f>I24+I18+I13</f>
         <v>256584.65073800003</v>
       </c>
-      <c r="J25" s="134">
+      <c r="J25" s="159">
         <f>I25/I$11</f>
         <v>1.7513064847976836</v>
       </c>
     </row>
     <row r="26" spans="2:10" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="143"/>
-      <c r="C26" s="136"/>
-      <c r="D26" s="144"/>
-      <c r="E26" s="133"/>
-      <c r="F26" s="146"/>
-      <c r="G26" s="148"/>
-      <c r="H26" s="150"/>
-      <c r="I26" s="133"/>
-      <c r="J26" s="135"/>
+      <c r="B26" s="168"/>
+      <c r="C26" s="161"/>
+      <c r="D26" s="169"/>
+      <c r="E26" s="158"/>
+      <c r="F26" s="171"/>
+      <c r="G26" s="173"/>
+      <c r="H26" s="175"/>
+      <c r="I26" s="158"/>
+      <c r="J26" s="160"/>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="B13:B17"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="I25:I26"/>
     <mergeCell ref="J25:J26"/>
     <mergeCell ref="C9:D9"/>
@@ -3416,6 +3401,21 @@
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="C23:D23"/>
+    <mergeCell ref="B13:B17"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -3532,44 +3532,44 @@
       <c r="E9" s="96"/>
     </row>
     <row r="10" spans="2:10" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="187" t="s">
+      <c r="C10" s="196" t="s">
         <v>147</v>
       </c>
-      <c r="D10" s="188"/>
-      <c r="E10" s="179">
+      <c r="D10" s="197"/>
+      <c r="E10" s="188">
         <v>46082</v>
       </c>
-      <c r="F10" s="180"/>
-      <c r="G10" s="177">
+      <c r="F10" s="189"/>
+      <c r="G10" s="186">
         <v>46113</v>
       </c>
-      <c r="H10" s="178"/>
-      <c r="I10" s="179">
+      <c r="H10" s="187"/>
+      <c r="I10" s="188">
         <v>46143</v>
       </c>
-      <c r="J10" s="180"/>
+      <c r="J10" s="189"/>
     </row>
     <row r="11" spans="2:10" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C11" s="181" t="s">
+      <c r="C11" s="190" t="s">
         <v>148</v>
       </c>
-      <c r="D11" s="182"/>
-      <c r="E11" s="183">
+      <c r="D11" s="191"/>
+      <c r="E11" s="192">
         <v>5444466</v>
       </c>
-      <c r="F11" s="184"/>
-      <c r="G11" s="185">
+      <c r="F11" s="193"/>
+      <c r="G11" s="194">
         <v>4985574</v>
       </c>
-      <c r="H11" s="186"/>
-      <c r="I11" s="183">
+      <c r="H11" s="195"/>
+      <c r="I11" s="192">
         <v>2965798</v>
       </c>
-      <c r="J11" s="184"/>
+      <c r="J11" s="193"/>
     </row>
     <row r="12" spans="2:10" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C12" s="173"/>
-      <c r="D12" s="174"/>
+      <c r="C12" s="151"/>
+      <c r="D12" s="152"/>
       <c r="E12" s="55" t="s">
         <v>149</v>
       </c>
@@ -3593,10 +3593,10 @@
       <c r="B13" s="129" t="s">
         <v>261</v>
       </c>
-      <c r="C13" s="175" t="s">
+      <c r="C13" s="198" t="s">
         <v>248</v>
       </c>
-      <c r="D13" s="176"/>
+      <c r="D13" s="154"/>
       <c r="E13" s="99">
         <v>1444502</v>
       </c>
@@ -3620,13 +3620,13 @@
       </c>
     </row>
     <row r="14" spans="2:10" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="152" t="s">
+      <c r="B14" s="177" t="s">
         <v>235</v>
       </c>
-      <c r="C14" s="189" t="s">
+      <c r="C14" s="185" t="s">
         <v>150</v>
       </c>
-      <c r="D14" s="189"/>
+      <c r="D14" s="185"/>
       <c r="E14" s="51">
         <f>'Calc - opperational'!G6</f>
         <v>453532.02</v>
@@ -3653,11 +3653,11 @@
       </c>
     </row>
     <row r="15" spans="2:10" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="152"/>
-      <c r="C15" s="189" t="s">
+      <c r="B15" s="177"/>
+      <c r="C15" s="185" t="s">
         <v>239</v>
       </c>
-      <c r="D15" s="189"/>
+      <c r="D15" s="185"/>
       <c r="E15" s="51">
         <f>'Calc - opperational'!G11</f>
         <v>11000</v>
@@ -3684,11 +3684,11 @@
       </c>
     </row>
     <row r="16" spans="2:10" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="152"/>
-      <c r="C16" s="189" t="s">
+      <c r="B16" s="177"/>
+      <c r="C16" s="185" t="s">
         <v>242</v>
       </c>
-      <c r="D16" s="189"/>
+      <c r="D16" s="185"/>
       <c r="E16" s="81">
         <f>'Calc - opperational'!D14</f>
         <v>185372</v>
@@ -3715,11 +3715,11 @@
       </c>
     </row>
     <row r="17" spans="2:10" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="152"/>
-      <c r="C17" s="189" t="s">
+      <c r="B17" s="177"/>
+      <c r="C17" s="185" t="s">
         <v>238</v>
       </c>
-      <c r="D17" s="189"/>
+      <c r="D17" s="185"/>
       <c r="E17" s="94">
         <f>E11*F17</f>
         <v>653335.91999999993</v>
@@ -3743,11 +3743,11 @@
       </c>
     </row>
     <row r="18" spans="2:10" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="137" t="s">
+      <c r="B18" s="162" t="s">
         <v>234</v>
       </c>
-      <c r="C18" s="138"/>
-      <c r="D18" s="139"/>
+      <c r="C18" s="163"/>
+      <c r="D18" s="164"/>
       <c r="E18" s="38">
         <f>SUM(E14:E17)</f>
         <v>1303239.94</v>
@@ -3774,13 +3774,13 @@
       </c>
     </row>
     <row r="19" spans="2:10" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="152" t="s">
+      <c r="B19" s="177" t="s">
         <v>236</v>
       </c>
-      <c r="C19" s="189" t="s">
+      <c r="C19" s="185" t="s">
         <v>4</v>
       </c>
-      <c r="D19" s="189"/>
+      <c r="D19" s="185"/>
       <c r="E19" s="81">
         <f>'Calc - opperational'!D23</f>
         <v>1581977.6400000001</v>
@@ -3807,11 +3807,11 @@
       </c>
     </row>
     <row r="20" spans="2:10" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="152"/>
-      <c r="C20" s="189" t="s">
+      <c r="B20" s="177"/>
+      <c r="C20" s="185" t="s">
         <v>151</v>
       </c>
-      <c r="D20" s="189"/>
+      <c r="D20" s="185"/>
       <c r="E20" s="81">
         <f>'Calc - opperational'!D31</f>
         <v>213619.19</v>
@@ -3838,11 +3838,11 @@
       </c>
     </row>
     <row r="21" spans="2:10" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="152"/>
-      <c r="C21" s="189" t="s">
+      <c r="B21" s="177"/>
+      <c r="C21" s="185" t="s">
         <v>152</v>
       </c>
-      <c r="D21" s="189"/>
+      <c r="D21" s="185"/>
       <c r="E21" s="81">
         <f>'Calc - opperational'!D42</f>
         <v>1705089.1799999997</v>
@@ -3869,11 +3869,11 @@
       </c>
     </row>
     <row r="22" spans="2:10" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="152"/>
-      <c r="C22" s="189" t="s">
+      <c r="B22" s="177"/>
+      <c r="C22" s="185" t="s">
         <v>153</v>
       </c>
-      <c r="D22" s="189"/>
+      <c r="D22" s="185"/>
       <c r="E22" s="81">
         <f>'Calc - opperational'!D49</f>
         <v>14068.85</v>
@@ -3900,11 +3900,11 @@
       </c>
     </row>
     <row r="23" spans="2:10" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="153"/>
-      <c r="C23" s="189" t="s">
+      <c r="B23" s="178"/>
+      <c r="C23" s="185" t="s">
         <v>154</v>
       </c>
-      <c r="D23" s="189"/>
+      <c r="D23" s="185"/>
       <c r="E23" s="81">
         <f>'Calc - opperational'!D52</f>
         <v>110584.91</v>
@@ -3931,11 +3931,11 @@
       </c>
     </row>
     <row r="24" spans="2:10" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="137" t="s">
+      <c r="B24" s="162" t="s">
         <v>237</v>
       </c>
-      <c r="C24" s="138"/>
-      <c r="D24" s="138"/>
+      <c r="C24" s="163"/>
+      <c r="D24" s="163"/>
       <c r="E24" s="49">
         <f>E23+E22+E21+E20+E19</f>
         <v>3625339.7699999996</v>
@@ -3962,63 +3962,49 @@
       </c>
     </row>
     <row r="25" spans="2:10" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="140" t="s">
+      <c r="B25" s="165" t="s">
         <v>240</v>
       </c>
-      <c r="C25" s="141"/>
-      <c r="D25" s="141"/>
-      <c r="E25" s="192">
+      <c r="C25" s="166"/>
+      <c r="D25" s="166"/>
+      <c r="E25" s="181">
         <f>E24+E18+E13</f>
         <v>6373081.709999999</v>
       </c>
-      <c r="F25" s="134">
+      <c r="F25" s="159">
         <f t="shared" si="3"/>
         <v>1.1705613938997872</v>
       </c>
-      <c r="G25" s="194">
+      <c r="G25" s="183">
         <f>G24+G18+G13</f>
         <v>6339231.6600000001</v>
       </c>
-      <c r="H25" s="190">
+      <c r="H25" s="179">
         <f>G25/G$11</f>
         <v>1.2715149068091258</v>
       </c>
-      <c r="I25" s="192">
+      <c r="I25" s="181">
         <f>I24+I18+I13</f>
         <v>5194021.2700000005</v>
       </c>
-      <c r="J25" s="134">
+      <c r="J25" s="159">
         <f>I25/I$11</f>
         <v>1.7513064847976836</v>
       </c>
     </row>
     <row r="26" spans="2:10" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="143"/>
-      <c r="C26" s="136"/>
-      <c r="D26" s="136"/>
-      <c r="E26" s="193"/>
-      <c r="F26" s="135"/>
-      <c r="G26" s="195"/>
-      <c r="H26" s="191"/>
-      <c r="I26" s="193"/>
-      <c r="J26" s="135"/>
+      <c r="B26" s="168"/>
+      <c r="C26" s="161"/>
+      <c r="D26" s="161"/>
+      <c r="E26" s="182"/>
+      <c r="F26" s="160"/>
+      <c r="G26" s="184"/>
+      <c r="H26" s="180"/>
+      <c r="I26" s="182"/>
+      <c r="J26" s="160"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="B19:B23"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B25:D26"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="F25:F26"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="G10:H10"/>
     <mergeCell ref="I10:J10"/>
@@ -4035,6 +4021,20 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="C17:D17"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="B19:B23"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B25:D26"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="F25:F26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -4064,67 +4064,67 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="187" t="s">
+      <c r="B2" s="196" t="s">
         <v>147</v>
       </c>
-      <c r="C2" s="188"/>
-      <c r="D2" s="179">
+      <c r="C2" s="197"/>
+      <c r="D2" s="188">
         <v>46082</v>
       </c>
-      <c r="E2" s="180"/>
-      <c r="F2" s="202"/>
-      <c r="G2" s="179">
+      <c r="E2" s="189"/>
+      <c r="F2" s="199"/>
+      <c r="G2" s="188">
         <v>46113</v>
       </c>
-      <c r="H2" s="180"/>
-      <c r="I2" s="202"/>
-      <c r="J2" s="179">
+      <c r="H2" s="189"/>
+      <c r="I2" s="199"/>
+      <c r="J2" s="188">
         <v>46143</v>
       </c>
-      <c r="K2" s="180"/>
-      <c r="L2" s="202"/>
+      <c r="K2" s="189"/>
+      <c r="L2" s="199"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B3" s="181" t="s">
+      <c r="B3" s="190" t="s">
         <v>148</v>
       </c>
-      <c r="C3" s="182"/>
-      <c r="D3" s="183">
+      <c r="C3" s="191"/>
+      <c r="D3" s="192">
         <v>5444466</v>
       </c>
-      <c r="E3" s="184"/>
-      <c r="F3" s="201"/>
-      <c r="G3" s="183">
+      <c r="E3" s="193"/>
+      <c r="F3" s="200"/>
+      <c r="G3" s="192">
         <v>4985574</v>
       </c>
-      <c r="H3" s="184"/>
-      <c r="I3" s="201"/>
-      <c r="J3" s="183">
+      <c r="H3" s="193"/>
+      <c r="I3" s="200"/>
+      <c r="J3" s="192">
         <v>2965798</v>
       </c>
-      <c r="K3" s="184"/>
-      <c r="L3" s="201"/>
+      <c r="K3" s="193"/>
+      <c r="L3" s="200"/>
     </row>
     <row r="4" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="193" t="s">
+      <c r="B4" s="182" t="s">
         <v>232</v>
       </c>
-      <c r="C4" s="206"/>
-      <c r="D4" s="198">
+      <c r="C4" s="204"/>
+      <c r="D4" s="201">
         <v>1520694</v>
       </c>
-      <c r="E4" s="199"/>
-      <c r="F4" s="200"/>
-      <c r="G4" s="198">
+      <c r="E4" s="202"/>
+      <c r="F4" s="203"/>
+      <c r="G4" s="201">
         <v>1807902</v>
       </c>
-      <c r="H4" s="199"/>
-      <c r="I4" s="200"/>
-      <c r="J4" s="198">
+      <c r="H4" s="202"/>
+      <c r="I4" s="203"/>
+      <c r="J4" s="201">
         <v>1081464</v>
       </c>
-      <c r="K4" s="199"/>
-      <c r="L4" s="200"/>
+      <c r="K4" s="202"/>
+      <c r="L4" s="203"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D5" s="55" t="s">
@@ -4156,13 +4156,13 @@
       </c>
     </row>
     <row r="6" spans="1:12" s="45" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="196" t="s">
+      <c r="A6" s="208" t="s">
         <v>235</v>
       </c>
-      <c r="B6" s="138" t="s">
+      <c r="B6" s="163" t="s">
         <v>150</v>
       </c>
-      <c r="C6" s="138"/>
+      <c r="C6" s="163"/>
       <c r="D6" s="44">
         <f>SUM(D7:D9)</f>
         <v>137785.1</v>
@@ -4201,7 +4201,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="197"/>
+      <c r="A7" s="209"/>
       <c r="C7" t="s">
         <v>19</v>
       </c>
@@ -4243,7 +4243,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="197"/>
+      <c r="A8" s="209"/>
       <c r="C8" t="s">
         <v>28</v>
       </c>
@@ -4285,7 +4285,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="197"/>
+      <c r="A9" s="209"/>
       <c r="C9" t="s">
         <v>103</v>
       </c>
@@ -4318,11 +4318,11 @@
       </c>
     </row>
     <row r="10" spans="1:12" s="45" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="197"/>
-      <c r="B10" s="138" t="s">
+      <c r="A10" s="209"/>
+      <c r="B10" s="163" t="s">
         <v>239</v>
       </c>
-      <c r="C10" s="138"/>
+      <c r="C10" s="163"/>
       <c r="D10" s="47">
         <f>SUM(D11:D13)</f>
         <v>0</v>
@@ -4351,7 +4351,7 @@
         <f t="shared" ref="J10" si="4">SUM(J11:J13)</f>
         <v>56.71</v>
       </c>
-      <c r="K10" s="217">
+      <c r="K10" s="133">
         <f>J10/J$3</f>
         <v>1.9121329234155528E-5</v>
       </c>
@@ -4361,7 +4361,7 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="197"/>
+      <c r="A11" s="209"/>
       <c r="C11" t="s">
         <v>83</v>
       </c>
@@ -4399,7 +4399,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="197"/>
+      <c r="A12" s="209"/>
       <c r="C12" t="s">
         <v>266</v>
       </c>
@@ -4421,7 +4421,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J12" s="216">
+      <c r="J12" s="132">
         <v>56.71</v>
       </c>
       <c r="K12" s="54">
@@ -4434,7 +4434,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="197"/>
+      <c r="A13" s="209"/>
       <c r="D13" s="41"/>
       <c r="E13" s="13"/>
       <c r="F13" s="42"/>
@@ -4446,11 +4446,11 @@
       <c r="L13" s="71"/>
     </row>
     <row r="14" spans="1:12" s="45" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="197"/>
-      <c r="B14" s="138" t="s">
+      <c r="A14" s="209"/>
+      <c r="B14" s="163" t="s">
         <v>242</v>
       </c>
-      <c r="C14" s="138"/>
+      <c r="C14" s="163"/>
       <c r="D14" s="49">
         <f>SUM(D15:D18)</f>
         <v>185372</v>
@@ -4489,7 +4489,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="197"/>
+      <c r="A15" s="209"/>
       <c r="C15" t="s">
         <v>225</v>
       </c>
@@ -4531,7 +4531,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="197"/>
+      <c r="A16" s="209"/>
       <c r="C16" t="s">
         <v>224</v>
       </c>
@@ -4573,7 +4573,7 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="197"/>
+      <c r="A17" s="209"/>
       <c r="C17" t="s">
         <v>227</v>
       </c>
@@ -4597,7 +4597,7 @@
       </c>
     </row>
     <row r="18" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="197"/>
+      <c r="A18" s="209"/>
       <c r="D18" s="41"/>
       <c r="E18" s="13"/>
       <c r="F18" s="42"/>
@@ -4609,11 +4609,11 @@
       <c r="L18" s="71"/>
     </row>
     <row r="19" spans="1:12" s="45" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="197"/>
-      <c r="B19" s="138" t="s">
+      <c r="A19" s="209"/>
+      <c r="B19" s="163" t="s">
         <v>238</v>
       </c>
-      <c r="C19" s="138"/>
+      <c r="C19" s="163"/>
       <c r="D19" s="49">
         <f>SUM(D20:D20)</f>
         <v>641988.9</v>
@@ -4652,7 +4652,7 @@
       </c>
     </row>
     <row r="20" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="197"/>
+      <c r="A20" s="209"/>
       <c r="C20" t="s">
         <v>143</v>
       </c>
@@ -4694,11 +4694,11 @@
       </c>
     </row>
     <row r="21" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="137" t="s">
+      <c r="A21" s="162" t="s">
         <v>234</v>
       </c>
-      <c r="B21" s="138"/>
-      <c r="C21" s="139"/>
+      <c r="B21" s="163"/>
+      <c r="C21" s="164"/>
       <c r="D21" s="38">
         <f>D19+D14+D6</f>
         <v>965146</v>
@@ -4737,7 +4737,7 @@
       </c>
     </row>
     <row r="22" spans="1:12" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="203" t="s">
+      <c r="A22" s="205" t="s">
         <v>236</v>
       </c>
       <c r="B22" s="75"/>
@@ -4753,11 +4753,11 @@
       <c r="L22" s="80"/>
     </row>
     <row r="23" spans="1:12" s="45" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="204"/>
-      <c r="B23" s="138" t="s">
+      <c r="A23" s="206"/>
+      <c r="B23" s="163" t="s">
         <v>4</v>
       </c>
-      <c r="C23" s="138"/>
+      <c r="C23" s="163"/>
       <c r="D23" s="49">
         <f>SUM(D24:D30)</f>
         <v>1581977.6400000001</v>
@@ -4796,7 +4796,7 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="204"/>
+      <c r="A24" s="206"/>
       <c r="C24" t="s">
         <v>228</v>
       </c>
@@ -4838,7 +4838,7 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="204"/>
+      <c r="A25" s="206"/>
       <c r="C25" t="s">
         <v>229</v>
       </c>
@@ -4880,7 +4880,7 @@
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="204"/>
+      <c r="A26" s="206"/>
       <c r="C26" t="s">
         <v>5</v>
       </c>
@@ -4922,7 +4922,7 @@
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="204"/>
+      <c r="A27" s="206"/>
       <c r="C27" t="s">
         <v>12</v>
       </c>
@@ -4964,7 +4964,7 @@
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="204"/>
+      <c r="A28" s="206"/>
       <c r="C28" t="s">
         <v>53</v>
       </c>
@@ -5006,7 +5006,7 @@
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="204"/>
+      <c r="A29" s="206"/>
       <c r="C29" t="s">
         <v>55</v>
       </c>
@@ -5048,7 +5048,7 @@
       </c>
     </row>
     <row r="30" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="204"/>
+      <c r="A30" s="206"/>
       <c r="D30" s="41"/>
       <c r="E30" s="13"/>
       <c r="F30" s="42"/>
@@ -5060,11 +5060,11 @@
       <c r="L30" s="71"/>
     </row>
     <row r="31" spans="1:12" s="45" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="204"/>
-      <c r="B31" s="138" t="s">
+      <c r="A31" s="206"/>
+      <c r="B31" s="163" t="s">
         <v>151</v>
       </c>
-      <c r="C31" s="138"/>
+      <c r="C31" s="163"/>
       <c r="D31" s="49">
         <f>SUM(D32:D41)</f>
         <v>213619.19</v>
@@ -5103,7 +5103,7 @@
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="204"/>
+      <c r="A32" s="206"/>
       <c r="C32" t="s">
         <v>49</v>
       </c>
@@ -5145,7 +5145,7 @@
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" s="204"/>
+      <c r="A33" s="206"/>
       <c r="C33" t="s">
         <v>51</v>
       </c>
@@ -5187,7 +5187,7 @@
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" s="204"/>
+      <c r="A34" s="206"/>
       <c r="C34" t="s">
         <v>16</v>
       </c>
@@ -5229,7 +5229,7 @@
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" s="204"/>
+      <c r="A35" s="206"/>
       <c r="C35" t="s">
         <v>35</v>
       </c>
@@ -5271,7 +5271,7 @@
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="204"/>
+      <c r="A36" s="206"/>
       <c r="C36" t="s">
         <v>45</v>
       </c>
@@ -5313,7 +5313,7 @@
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A37" s="204"/>
+      <c r="A37" s="206"/>
       <c r="C37" t="s">
         <v>60</v>
       </c>
@@ -5355,7 +5355,7 @@
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A38" s="204"/>
+      <c r="A38" s="206"/>
       <c r="C38" t="s">
         <v>96</v>
       </c>
@@ -5388,7 +5388,7 @@
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A39" s="204"/>
+      <c r="A39" s="206"/>
       <c r="C39" t="s">
         <v>86</v>
       </c>
@@ -5421,7 +5421,7 @@
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A40" s="204"/>
+      <c r="A40" s="206"/>
       <c r="C40" t="s">
         <v>114</v>
       </c>
@@ -5445,7 +5445,7 @@
       </c>
     </row>
     <row r="41" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="204"/>
+      <c r="A41" s="206"/>
       <c r="D41" s="41"/>
       <c r="E41" s="13"/>
       <c r="F41" s="42"/>
@@ -5457,11 +5457,11 @@
       <c r="L41" s="71"/>
     </row>
     <row r="42" spans="1:12" s="45" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="204"/>
-      <c r="B42" s="138" t="s">
+      <c r="A42" s="206"/>
+      <c r="B42" s="163" t="s">
         <v>152</v>
       </c>
-      <c r="C42" s="138"/>
+      <c r="C42" s="163"/>
       <c r="D42" s="49">
         <f>SUM(D43:D48)</f>
         <v>1705089.1799999997</v>
@@ -5500,7 +5500,7 @@
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="204"/>
+      <c r="A43" s="206"/>
       <c r="C43" t="s">
         <v>22</v>
       </c>
@@ -5542,7 +5542,7 @@
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A44" s="204"/>
+      <c r="A44" s="206"/>
       <c r="C44" t="s">
         <v>25</v>
       </c>
@@ -5584,7 +5584,7 @@
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A45" s="204"/>
+      <c r="A45" s="206"/>
       <c r="C45" t="s">
         <v>8</v>
       </c>
@@ -5626,7 +5626,7 @@
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A46" s="204"/>
+      <c r="A46" s="206"/>
       <c r="C46" t="s">
         <v>231</v>
       </c>
@@ -5668,7 +5668,7 @@
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A47" s="204"/>
+      <c r="A47" s="206"/>
       <c r="C47" t="s">
         <v>67</v>
       </c>
@@ -5710,7 +5710,7 @@
       </c>
     </row>
     <row r="48" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="204"/>
+      <c r="A48" s="206"/>
       <c r="D48" s="41"/>
       <c r="E48" s="13"/>
       <c r="F48" s="42"/>
@@ -5722,11 +5722,11 @@
       <c r="L48" s="71"/>
     </row>
     <row r="49" spans="1:12" s="45" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="204"/>
-      <c r="B49" s="138" t="s">
+      <c r="A49" s="206"/>
+      <c r="B49" s="163" t="s">
         <v>153</v>
       </c>
-      <c r="C49" s="138"/>
+      <c r="C49" s="163"/>
       <c r="D49" s="49">
         <f>SUM(D50:D51)</f>
         <v>14068.85</v>
@@ -5765,7 +5765,7 @@
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A50" s="204"/>
+      <c r="A50" s="206"/>
       <c r="C50" t="s">
         <v>63</v>
       </c>
@@ -5807,7 +5807,7 @@
       </c>
     </row>
     <row r="51" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="204"/>
+      <c r="A51" s="206"/>
       <c r="C51" t="s">
         <v>134</v>
       </c>
@@ -5831,11 +5831,11 @@
       </c>
     </row>
     <row r="52" spans="1:12" s="45" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="204"/>
-      <c r="B52" s="138" t="s">
+      <c r="A52" s="206"/>
+      <c r="B52" s="163" t="s">
         <v>154</v>
       </c>
-      <c r="C52" s="138"/>
+      <c r="C52" s="163"/>
       <c r="D52" s="49">
         <f>SUM(D53:D55)</f>
         <v>110584.91</v>
@@ -5874,7 +5874,7 @@
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A53" s="204"/>
+      <c r="A53" s="206"/>
       <c r="C53" t="s">
         <v>38</v>
       </c>
@@ -5916,7 +5916,7 @@
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A54" s="204"/>
+      <c r="A54" s="206"/>
       <c r="C54" t="s">
         <v>69</v>
       </c>
@@ -5958,7 +5958,7 @@
       </c>
     </row>
     <row r="55" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="205"/>
+      <c r="A55" s="207"/>
       <c r="D55" s="41"/>
       <c r="E55" s="13"/>
       <c r="F55" s="42"/>
@@ -5970,11 +5970,11 @@
       <c r="L55" s="71"/>
     </row>
     <row r="56" spans="1:12" s="45" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="137" t="s">
+      <c r="A56" s="162" t="s">
         <v>237</v>
       </c>
-      <c r="B56" s="138"/>
-      <c r="C56" s="138"/>
+      <c r="B56" s="163"/>
+      <c r="C56" s="163"/>
       <c r="D56" s="49">
         <f>D52+D49+D42+D31+D23</f>
         <v>3625339.7699999996</v>
@@ -6013,76 +6013,78 @@
       </c>
     </row>
     <row r="57" spans="1:12" s="50" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="140" t="s">
+      <c r="A57" s="165" t="s">
         <v>240</v>
       </c>
-      <c r="B57" s="141"/>
-      <c r="C57" s="141"/>
-      <c r="D57" s="192">
+      <c r="B57" s="166"/>
+      <c r="C57" s="166"/>
+      <c r="D57" s="181">
         <f>D56+D21</f>
         <v>4590485.7699999996</v>
       </c>
-      <c r="E57" s="134">
+      <c r="E57" s="159">
         <f t="shared" ref="E57" si="35">D57/$D$3</f>
         <v>0.84314710937675053</v>
       </c>
-      <c r="F57" s="145">
+      <c r="F57" s="170">
         <f t="shared" ref="F57" si="36">D57/$D$4</f>
         <v>3.0186781627335937</v>
       </c>
-      <c r="G57" s="192">
+      <c r="G57" s="181">
         <f t="shared" ref="G57" si="37">G56+G21</f>
         <v>4727364.2699999996</v>
       </c>
-      <c r="H57" s="134">
+      <c r="H57" s="159">
         <f>G57/G$3</f>
         <v>0.94820862552636864</v>
       </c>
-      <c r="I57" s="145">
+      <c r="I57" s="170">
         <f>G57/G$4</f>
         <v>2.6148343604907787</v>
       </c>
-      <c r="J57" s="192">
+      <c r="J57" s="181">
         <f t="shared" ref="J57" si="38">J56+J21</f>
         <v>4089184.0400000005</v>
       </c>
-      <c r="K57" s="134">
+      <c r="K57" s="159">
         <f>J57/J$3</f>
         <v>1.3787803619801484</v>
       </c>
-      <c r="L57" s="145">
+      <c r="L57" s="170">
         <f>J57/J$4</f>
         <v>3.7811559515619573</v>
       </c>
     </row>
     <row r="58" spans="1:12" s="32" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="143"/>
-      <c r="B58" s="136"/>
-      <c r="C58" s="136"/>
-      <c r="D58" s="193"/>
-      <c r="E58" s="135"/>
-      <c r="F58" s="146"/>
-      <c r="G58" s="193"/>
-      <c r="H58" s="135"/>
-      <c r="I58" s="146"/>
-      <c r="J58" s="193"/>
-      <c r="K58" s="135"/>
-      <c r="L58" s="146"/>
+      <c r="A58" s="168"/>
+      <c r="B58" s="161"/>
+      <c r="C58" s="161"/>
+      <c r="D58" s="182"/>
+      <c r="E58" s="160"/>
+      <c r="F58" s="171"/>
+      <c r="G58" s="182"/>
+      <c r="H58" s="160"/>
+      <c r="I58" s="171"/>
+      <c r="J58" s="182"/>
+      <c r="K58" s="160"/>
+      <c r="L58" s="171"/>
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="L57:L58"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="J57:J58"/>
-    <mergeCell ref="K57:K58"/>
-    <mergeCell ref="G57:G58"/>
-    <mergeCell ref="H57:H58"/>
-    <mergeCell ref="I57:I58"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="A6:A20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="A22:A55"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A57:C58"/>
+    <mergeCell ref="D57:D58"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B52:C52"/>
     <mergeCell ref="E57:E58"/>
     <mergeCell ref="F57:F58"/>
     <mergeCell ref="B2:C2"/>
@@ -6092,20 +6094,18 @@
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B19:C19"/>
-    <mergeCell ref="A22:A55"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A57:C58"/>
-    <mergeCell ref="D57:D58"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="A6:A20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="G57:G58"/>
+    <mergeCell ref="H57:H58"/>
+    <mergeCell ref="I57:I58"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="L57:L58"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="J57:J58"/>
+    <mergeCell ref="K57:K58"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -7481,30 +7481,30 @@
       </c>
     </row>
     <row r="40" spans="2:7" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B40" s="207" t="s">
+      <c r="B40" s="210" t="s">
         <v>143</v>
       </c>
-      <c r="C40" s="209"/>
+      <c r="C40" s="212"/>
       <c r="D40" s="63" t="s">
         <v>144</v>
       </c>
-      <c r="E40" s="211" t="s">
+      <c r="E40" s="214" t="s">
         <v>146</v>
       </c>
-      <c r="F40" s="213">
+      <c r="F40" s="216">
         <v>641988.9</v>
       </c>
-      <c r="G40" s="213"/>
+      <c r="G40" s="216"/>
     </row>
     <row r="41" spans="2:7" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B41" s="208"/>
-      <c r="C41" s="210"/>
+      <c r="B41" s="211"/>
+      <c r="C41" s="213"/>
       <c r="D41" s="64" t="s">
         <v>145</v>
       </c>
-      <c r="E41" s="212"/>
-      <c r="F41" s="214"/>
-      <c r="G41" s="214"/>
+      <c r="E41" s="215"/>
+      <c r="F41" s="217"/>
+      <c r="G41" s="217"/>
     </row>
   </sheetData>
   <mergeCells count="5">
